--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:31</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -78,12 +78,12 @@
     <t xml:space="preserve">San Juan de la Costa</t>
   </si>
   <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chonchi</t>
   </si>
   <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -797,7 +797,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10203</v>
+        <v>10102</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2024</v>
@@ -814,7 +814,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10102</v>
+        <v>10203</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2024_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 08:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
